--- a/outputs_part1/Results for Part I-SAAM.xlsx
+++ b/outputs_part1/Results for Part I-SAAM.xlsx
@@ -313,12 +313,12 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5334000" cy="2381250"/>
+    <ext cx="6858000" cy="3429000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -721,7 +721,7 @@
         <v>0.081848026323112</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.04671291483430778</v>
+        <v>0.0467129148343078</v>
       </c>
       <c r="E3" s="22" t="n">
         <v>41640</v>
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1580881595373777</v>
+        <v>0.1580881595373778</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.1376550850808409</v>
+        <v>0.137655085080841</v>
       </c>
       <c r="E4" s="9" t="n">
         <v>41671</v>
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07162031922100542</v>
+        <v>0.0716203192210054</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.03783078922681926</v>
+        <v>0.0378307892268192</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>41699</v>
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5177366006576869</v>
+        <v>0.5177366006576867</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.3393475424963387</v>
+        <v>0.3393475424963389</v>
       </c>
       <c r="E6" s="9" t="n">
         <v>41730</v>
